--- a/outputs/evaluation/decision/v1/CF_M08/run_3/CF_M08_decision_eval.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M08/run_3/CF_M08_decision_eval.xlsx
@@ -450,13 +450,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5714</v>
+        <v>0.375</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3333</v>
+        <v>0.25</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8250999999999999</v>
+        <v>0.7981</v>
       </c>
     </row>
     <row r="5">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.3333</v>
+        <v>0.6667</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5714</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="8">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3333</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="9">
@@ -726,19 +726,19 @@
         <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -755,28 +755,28 @@
         <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" t="n">
         <v>4</v>
       </c>
-      <c r="H3" t="n">
-        <v>4</v>
-      </c>
-      <c r="I3" t="n">
-        <v>6</v>
-      </c>
       <c r="J3" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -792,28 +792,28 @@
         <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
         <v>3</v>
@@ -829,22 +829,22 @@
         <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7514</v>
+        <v>0.7858000000000001</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -992,7 +992,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1009,32 +1009,32 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Next.js is a framework for building web applications that supports both client-side and server-side rendering. [...] It has been used to facilitate the translation of Next.js applications into multiple languages.</t>
+          <t>Next.js is a framework for building web applications that supports both client-side and server-side rendering, allowing to choose the best strategy according to the needs of the application.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>R_02, R_16, R_17, C_01</t>
+          <t>R_18, C_02</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>AU_03, AU_06</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>44, 75</t>
+          <t>44, 45</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -1064,11 +1064,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M08_AD10</t>
+          <t>CF_M08_AD12</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.783</v>
+        <v>0.7936</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1077,7 +1077,7 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1094,42 +1094,42 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3333</v>
+        <v>0.5</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Prisma is an ORM tool used to simplify database access and management. [...] Prisma is designed to simplify database access and management in Node.js and TypeScript applications.</t>
+          <t>Prisma is an ORM tool used to simplify database access and management.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>R_24, R_25, C_05</t>
+          <t>C_05</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>AU_04, AU_07, AU_08</t>
+          <t>AU_08, AU_07</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>42, 50</t>
+          <t>50</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>It is designed to simplify access and database management</t>
+          <t>Prisma Studio is a visual tool to explore and edit data in the database. It provides a graphical interface to visualize and manipulate the data, facilitating development and debugging.</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>*CF_M08_C22</t>
+          <t>*CF_M08_C24</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1149,11 +1149,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CF_M08_AD03</t>
+          <t>CF_M08_AD01</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8817</v>
+        <v>0.8149</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
         <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -1182,21 +1182,19 @@
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Traefik is a modern reverse proxy and load balancer designed to manage incoming and outgoing HTTP and HTTPS traffic. [...] HTTPS encrypts the data transmitted between the clients and the server, protecting the integrity and confidentiality of the information.</t>
+          <t>Traefik acts as a reverse proxy and load balancer, managing HTTP and HTTPS request routing, improving availability and responsiveness.</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>R_20, R_21, C_03</t>
+          <t>R_20, R_22, C_03, C_04</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1211,106 +1209,21 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>HTTPS encrypts the data transmitted between the clients and the server, protecting the integrity and confidentiality of the information.</t>
+          <t>Load Balancer: Distributes traffic between multiple instances of a service, improving the availability and responsiveness of the application</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>*CF_M08_C11, *CF_M08_C12</t>
+          <t>CF_M08_C08, *CF_M08_C09</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>CF_M08_AU22</t>
+          <t>CF_M08_AU03</t>
         </is>
       </c>
       <c r="U4" t="n">
         <v>43</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AD_05</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>CF_M08_AD08</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.8844</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. [...] React is an open-source JavaScript library designed to build user interfaces.</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>R_18, R_19, C_02</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>P_02, AU_15</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>47, 66</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>React is an open source JavaScript library designed to build user interfaces (UI) efficiently and flexibly</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>*CF_M08_C18, *CF_M08_C19</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>CF_M08_AU06</t>
-        </is>
-      </c>
-      <c r="U5" t="n">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1324,7 +1237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1372,17 +1285,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The architecture implemented for the development of the Revivack project system is a microservices-based architecture. [...] In the case of this application, such services are executed in Amazon EC2 instances and are managed by Docker, which manages the execution of the containers.</t>
+          <t>The architecture implemented for the development of the Revivack project system is a microservices-based architecture.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>R_28, R_29, C_07</t>
+          <t>R_28, C_07</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>P_01, AU_09</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1392,81 +1305,151 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M08_AD01</t>
+          <t>CF_M08_AD07</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6422</v>
+        <v>0.6187</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance. [...] In the case of this application, it has been used, for example, to manage the PrismaClient instance.</t>
+          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components, promoting modularity, code reuse, and maintainability.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>C_04, Robustness</t>
+          <t>C_05</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>P_04, AU_08</t>
+          <t>P_02</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M08_AD10</t>
+          <t>CF_M08_AD09</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.6315</v>
+        <v>0.7297</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>AD_06</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>The Observer pattern establishes a one-to-many relationship between objects, allowing them to react appropriately to state changes.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>C_05</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>P_03</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CF_M08_AD01</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6169</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>AD_07</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Sentry is used to track and manage errors in the application. [...] Sentry has been used to capture and report errors and exceptions, facilitating debugging and improving application stability.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>R_24, R_25, C_05</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>AU_13</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>42, 74</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>CF_M08_AD01</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>0.6092</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance, used to manage shared resources like database connections.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>C_05</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>P_04</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CF_M08_AD10</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.671</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AD_08</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Docker is a containerization platform used to manage the execution of the application services, allowing to create an application and package it together with its dependencies and libraries.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>C_05, C_06</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AU_09</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CF_M08_AD07</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6291</v>
       </c>
     </row>
   </sheetData>
@@ -1480,7 +1463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1523,17 +1506,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M08_AD01</t>
+          <t>CF_M08_AD02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Load Balancer: Distributes traffic between multiple instances of a service, improving the availability and responsiveness of the application</t>
+          <t>Traefik opens port 80 to handle non-secure HTTP traffic re-
+directing this traffic to port 443 (HTTPS) to ensure that all communications are carried out safely.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CF_M08_C08, *CF_M08_C09</t>
+          <t>*CF_M08_C10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1550,29 +1534,28 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6758</v>
+        <v>0.7841</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M08_AD02</t>
+          <t>CF_M08_AD03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Traefik opens port 80 to handle non-secure HTTP traffic re-
-directing this traffic to port 443 (HTTPS) to ensure that all communications are carried out safely.</t>
+          <t>HTTPS encrypts the data transmitted between the clients and the server, protecting the integrity and confidentiality of the information.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>*CF_M08_C10</t>
+          <t>*CF_M08_C11, *CF_M08_C12</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CF_M08_AU03</t>
+          <t>CF_M08_AU22</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1584,7 +1567,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.8217</v>
+        <v>0.6564</v>
       </c>
     </row>
     <row r="4">
@@ -1613,11 +1596,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_08</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.5655</v>
+        <v>0.576</v>
       </c>
     </row>
     <row r="5">
@@ -1650,7 +1633,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.6649</v>
+        <v>0.6673</v>
       </c>
     </row>
     <row r="6">
@@ -1683,23 +1666,23 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.6852</v>
+        <v>0.697</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M08_AD09</t>
+          <t>CF_M08_AD08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>React allows developers to create dynamic and fast web applications by facilitating the creation of reusable and modular components</t>
+          <t>React is an open source JavaScript library designed to build user interfaces (UI) efficiently and flexibly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>*CF_M08_C20, *CF_M08_C21</t>
+          <t>*CF_M08_C18, *CF_M08_C19</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1716,56 +1699,56 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.8071</v>
+        <v>0.6963</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M08_AD11</t>
+          <t>CF_M08_AD09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Prisma is compatible with several databases, including PostgreSQL, MySQL, SQLite and SQL Server.</t>
+          <t>React allows developers to create dynamic and fast web applications by facilitating the creation of reusable and modular components</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>*CF_M08_C23</t>
+          <t>*CF_M08_C20, *CF_M08_C21</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CF_M08_AU09</t>
+          <t>CF_M08_AU06</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_05</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.7592</v>
+        <v>0.7297</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M08_AD12</t>
+          <t>CF_M08_AD10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Prisma Studio is a visual tool to explore and edit data in the database. It provides a graphical interface to visualize and manipulate the data, facilitating development and debugging.</t>
+          <t>It is designed to simplify access and database management</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>*CF_M08_C24</t>
+          <t>*CF_M08_C22</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1782,7 +1765,40 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.7669</v>
+        <v>0.7812</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CF_M08_AD11</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Prisma is compatible with several databases, including PostgreSQL, MySQL, SQLite and SQL Server.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>*CF_M08_C23</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CF_M08_AU09</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>50</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>AD_04</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0.7723</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/decision/v1/CF_M08/run_3/CF_M08_decision_eval.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M08/run_3/CF_M08_decision_eval.xlsx
@@ -450,13 +450,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.375</v>
+        <v>0.3333</v>
       </c>
       <c r="C2" t="n">
-        <v>0.25</v>
+        <v>0.2143</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7981</v>
+        <v>0.7824</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6667</v>
+        <v>0.3167</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0.9637</v>
       </c>
     </row>
     <row r="8">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0.3333</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.375</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="8">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.25</v>
+        <v>0.2143</v>
       </c>
     </row>
     <row r="9">
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
@@ -752,10 +752,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
@@ -776,7 +776,7 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -789,10 +789,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -813,7 +813,7 @@
         <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K4" t="n">
         <v>3</v>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
@@ -838,7 +838,7 @@
         <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>3</v>
@@ -979,11 +979,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M08_AD05</t>
+          <t>CF_M08_AD11</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7858000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -992,7 +992,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1009,75 +1009,75 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Next.js is a framework for building web applications that supports both client-side and server-side rendering, allowing to choose the best strategy according to the needs of the application.</t>
+          <t>Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM7 (Object-Relational Mapping).</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>R_18, C_02</t>
+          <t>R_07, R_10, R_11, R_12, R_14, R_15, R_28, R_29, R_30, R_31, C_07</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>AU_03, AU_07, AU_08, AU_17, P_01</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>44, 45</t>
+          <t>42</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Next.js supports several styling methods, including CSS, Tailwind CSS and CSS-in-JS modules, offering flexibility in style management</t>
+          <t>Prisma is compatible with several databases, including PostgreSQL, MySQL, SQLite and SQL Server.</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>*CF_M08_C15</t>
+          <t>*CF_M08_C23</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>CF_M08_AU05</t>
+          <t>CF_M08_AU09</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M08_AD12</t>
+          <t>CF_M08_AD09</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.7936</v>
+        <v>0.7776</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1094,75 +1094,75 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Prisma is an ORM tool used to simplify database access and management.</t>
+          <t>Sirve la aplicación web mediante React.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>C_05</t>
+          <t>R_02, R_06, R_16, R_17, R_18, R_19, C_01, C_02</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>AU_08, AU_07</t>
+          <t>AU_03, AU_06, AU_15, P_01</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>42</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Prisma Studio is a visual tool to explore and edit data in the database. It provides a graphical interface to visualize and manipulate the data, facilitating development and debugging.</t>
+          <t>React allows developers to create dynamic and fast web applications by facilitating the creation of reusable and modular components</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>*CF_M08_C24</t>
+          <t>*CF_M08_C20, *CF_M08_C21</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>CF_M08_AU09</t>
+          <t>CF_M08_AU06</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CF_M08_AD01</t>
+          <t>CF_M08_AD13</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8149</v>
+        <v>0.8096</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -1185,45 +1185,45 @@
         <v>0.5</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0.891</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Traefik acts as a reverse proxy and load balancer, managing HTTP and HTTPS request routing, improving availability and responsiveness.</t>
+          <t>El patrón Singleton asegura que una clase tenga solo una instancia y proporciona un punto de acceso global a esa instancia. Se utiliza generalmente para gestionar recursos compartidos, como configuraciones, registros o conexiones a bases de datos, donde tener múltiples instancias podría llevar a estados inconsistentes o al uso ineficiente de recursos.</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>R_20, R_22, C_03, C_04</t>
+          <t>R_22, R_23, R_24, R_25, C_04, C_05</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>AU_02, AU_05</t>
+          <t>AU_08, P_04</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>67</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Load Balancer: Distributes traffic between multiple instances of a service, improving the availability and responsiveness of the application</t>
+          <t>It is generally used for manage shared resources, such as configurations, records or connections to databases data, where having multiple instances could lead to inconsistent states or usage resource inefficient.</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>CF_M08_C08, *CF_M08_C09</t>
+          <t>CF_M08_C06</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>CF_M08_AU03</t>
+          <t>CF_M08_P05</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>43</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1285,17 +1285,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The architecture implemented for the development of the Revivack project system is a microservices-based architecture.</t>
+          <t>Funciona como un proxy inverso y balanceador de carga. • Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js (System Service). • Expone los puertos 80 (HTTP) y 443 (HTTPS) al mundo exterior y redirige el tráfico a los servicios internos según las reglas definidas.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>R_28, C_07</t>
+          <t>R_22, R_23, C_04</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_01, AU_02, AU_05, AU_16, AU_23, AU_24, P_01</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1305,151 +1305,186 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M08_AD07</t>
+          <t>CF_M08_AD02</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6187</v>
+        <v>0.7491</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components, promoting modularity, code reuse, and maintainability.</t>
+          <t>Interactúa con varios servicios externos para funcionalidades específicas: ◦ Autenticación: Utiliza Google para la autenticación de usuarios. ◦ Almacenamiento en la nube: Utiliza Amazon S3 para almacenar y recuperar archivos. ◦ Procesamiento de pagos: Integra con Stripe para manejar pagos y suscripciones. ◦ Análisis: Implementa Google Analytics para rastrear y analizar el tráfico del sitio. ◦ Monitoreo de errores: Utiliza Sentry para rastrear y gestionar errores en la aplicación. ◦ Correo Electrónico: Se conecta a Brevo para crear, enviar y programar correos electrónicos.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>C_05</t>
+          <t>R_04, R_07, R_09, R_14, R_20, R_21, R_22, R_23, C_03, C_04</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_03, AU_19, AU_21, AU_22, AU_18, AU_20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M08_AD09</t>
+          <t>CF_M08_AD07</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.7297</v>
+        <v>0.6754</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Observer pattern establishes a one-to-many relationship between objects, allowing them to react appropriately to state changes.</t>
+          <t>Proporciona la base de datos relacional para almacenar los datos de la aplicación. • Se comunica directamente con Prisma para gestionar las consultas de la base de datos.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>C_05</t>
+          <t>R_28, R_29, C_07</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_04, AU_07, AU_17</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M08_AD01</t>
+          <t>CF_M08_AD11</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.6169</v>
+        <v>0.7517</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AD_07</t>
+          <t>AD_06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance, used to manage shared resources like database connections.</t>
+          <t>Cabe destacar que cada uno de estos servicios esta contenido en un contenedor de Docker.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>C_05</t>
+          <t>R_22, R_23, C_04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>AU_09, P_01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M08_AD10</t>
+          <t>CF_M08_AD14</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.671</v>
+        <v>0.629</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>AD_07</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>El patrón Component-Based se centra en la construcción de la interfaz de usuario mediante la creación de componentes independientes y reutilizables. Cada componente encapsula su propia lógica, estilos y estructura, lo que permite que estos se desarrollen, mantengan y prueben de manera aislada.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>R_18, R_24, R_25, C_02, C_05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>P_02</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CF_M08_AD14</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7347</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>AD_08</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Docker is a containerization platform used to manage the execution of the application services, allowing to create an application and package it together with its dependencies and libraries.</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>C_05, C_06</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>AU_09</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>El patrón Observer establece una relación de uno a muchos entre objetos, donde un objeto conocido como el sujeto mantiene una lista de otros objetos llamados observadores. Estos observadores se suscriben al sujeto para recibir notificaciones de cambios en su estado. Cuando el estado del sujeto cambia, notifica automáticamente a todos sus observadores, permitiendo que estos reaccionen adecuadamente.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>R_24, R_25, C_05</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>P_03</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>CF_M08_AD07</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>0.6291</v>
+      <c r="G7" t="n">
+        <v>0.6056</v>
       </c>
     </row>
   </sheetData>
@@ -1463,7 +1498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1506,56 +1541,56 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>CF_M08_AD01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Load Balancer: Distributes traffic between multiple instances of a service, improving the availability and responsiveness of the application</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CF_M08_C08, *CF_M08_C09</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CF_M08_AU03</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>43</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>AD_01</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7311</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>CF_M08_AD02</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Traefik opens port 80 to handle non-secure HTTP traffic re-
 directing this traffic to port 443 (HTTPS) to ensure that all communications are carried out safely.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>*CF_M08_C10</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>CF_M08_AU03</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>43</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>AD_02</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>0.7841</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CF_M08_AD03</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>HTTPS encrypts the data transmitted between the clients and the server, protecting the integrity and confidentiality of the information.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>*CF_M08_C11, *CF_M08_C12</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CF_M08_AU22</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1563,60 +1598,60 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.6564</v>
+        <v>0.7491</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M08_AD04</t>
+          <t>CF_M08_AD03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>This facilitates the creation of paths by simply adding files and folders inside the src directory.</t>
+          <t>HTTPS encrypts the data transmitted between the clients and the server, protecting the integrity and confidentiality of the information.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>*CF_M08_C14</t>
+          <t>*CF_M08_C11, *CF_M08_C12</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CF_M08_AU05</t>
+          <t>CF_M08_AU22</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AD_08</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.576</v>
+        <v>0.6475</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M08_AD06</t>
+          <t>CF_M08_AD04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>It includes automatic optimizations for images, fonts and scripts, improving the performance of the application.</t>
+          <t>This facilitates the creation of paths by simply adding files and folders inside the src directory.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>*CF_M08_C16</t>
+          <t>*CF_M08_C14</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1629,27 +1664,27 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_07</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.6673</v>
+        <v>0.5717</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M08_AD07</t>
+          <t>CF_M08_AD05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>This is useful for handling complex logic or interacting with databases and other services server side from components rendered on the client without having to write an API complete It is similar to a simulation of an API, allowing a simpler integration and direct from the server logic in the application.</t>
+          <t>Next.js supports several styling methods, including CSS, Tailwind CSS and CSS-in-JS modules, offering flexibility in style management</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>*CF_M08_C17</t>
+          <t>*CF_M08_C15</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1658,130 +1693,130 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.697</v>
+        <v>0.6253</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M08_AD08</t>
+          <t>CF_M08_AD06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>React is an open source JavaScript library designed to build user interfaces (UI) efficiently and flexibly</t>
+          <t>It includes automatic optimizations for images, fonts and scripts, improving the performance of the application.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>*CF_M08_C18, *CF_M08_C19</t>
+          <t>*CF_M08_C16</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CF_M08_AU06</t>
+          <t>CF_M08_AU05</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.6963</v>
+        <v>0.6293</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M08_AD09</t>
+          <t>CF_M08_AD07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>React allows developers to create dynamic and fast web applications by facilitating the creation of reusable and modular components</t>
+          <t>This is useful for handling complex logic or interacting with databases and other services server side from components rendered on the client without having to write an API complete It is similar to a simulation of an API, allowing a simpler integration and direct from the server logic in the application.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>*CF_M08_C20, *CF_M08_C21</t>
+          <t>*CF_M08_C17</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CF_M08_AU06</t>
+          <t>CF_M08_AU05</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_07</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.7297</v>
+        <v>0.6933</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M08_AD10</t>
+          <t>CF_M08_AD08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>It is designed to simplify access and database management</t>
+          <t>React is an open source JavaScript library designed to build user interfaces (UI) efficiently and flexibly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>*CF_M08_C22</t>
+          <t>*CF_M08_C18, *CF_M08_C19</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CF_M08_AU09</t>
+          <t>CF_M08_AU06</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.7812</v>
+        <v>0.761</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M08_AD11</t>
+          <t>CF_M08_AD10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Prisma is compatible with several databases, including PostgreSQL, MySQL, SQLite and SQL Server.</t>
+          <t>It is designed to simplify access and database management</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>*CF_M08_C23</t>
+          <t>*CF_M08_C22</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1794,11 +1829,77 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_05</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.7723</v>
+        <v>0.7136</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CF_M08_AD12</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Prisma Studio is a visual tool to explore and edit data in the database. It provides a graphical interface to visualize and manipulate the data, facilitating development and debugging.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>*CF_M08_C24</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CF_M08_AU09</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>50</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>AD_05</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0.7378</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CF_M08_AD14</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>This approach promotes modularity, code reuse and maintainability, facilitating the management of the application</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>*CF_M08_C21, CF_M08_C05</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CF_M08_P03</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>66</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>AD_07</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0.7347</v>
       </c>
     </row>
   </sheetData>
